--- a/Assets/Data/Dungeon0063.xlsx
+++ b/Assets/Data/Dungeon0063.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="8410" activeTab="3"/>
+    <workbookView windowWidth="18650" windowHeight="8390" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="3" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="25">
   <si>
     <t>Id</t>
   </si>
@@ -52,6 +52,9 @@
     <t>■</t>
   </si>
   <si>
+    <t>Ba</t>
+  </si>
+  <si>
     <t>No</t>
   </si>
   <si>
@@ -59,6 +62,9 @@
   </si>
   <si>
     <t>Mv</t>
+  </si>
+  <si>
+    <t>Mg</t>
   </si>
   <si>
     <t>Ev</t>
@@ -96,10 +102,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -117,13 +123,7 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -146,6 +146,105 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
@@ -161,101 +260,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -270,7 +276,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -288,73 +408,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -372,79 +438,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -466,9 +472,11 @@
     <border>
       <left/>
       <right/>
-      <top/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
       <bottom style="double">
-        <color rgb="FFFF8001"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -488,17 +496,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -514,6 +516,15 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -537,27 +548,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -569,145 +575,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="11" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="20" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -730,12 +736,12 @@
     <cellStyle name="通貨[0]" xfId="4" builtinId="7"/>
     <cellStyle name="40% - アクセント 5" xfId="5" builtinId="47"/>
     <cellStyle name="通貨" xfId="6" builtinId="4"/>
-    <cellStyle name="パーセント" xfId="7" builtinId="5"/>
-    <cellStyle name="ハイパーリンク" xfId="8" builtinId="8"/>
-    <cellStyle name="アクセント 2" xfId="9" builtinId="33"/>
-    <cellStyle name="訪問済ハイパーリンク" xfId="10" builtinId="9"/>
-    <cellStyle name="20% - アクセント 4" xfId="11" builtinId="42"/>
-    <cellStyle name="メモ" xfId="12" builtinId="10"/>
+    <cellStyle name="20% - アクセント 4" xfId="7" builtinId="42"/>
+    <cellStyle name="メモ" xfId="8" builtinId="10"/>
+    <cellStyle name="パーセント" xfId="9" builtinId="5"/>
+    <cellStyle name="ハイパーリンク" xfId="10" builtinId="8"/>
+    <cellStyle name="アクセント 2" xfId="11" builtinId="33"/>
+    <cellStyle name="訪問済ハイパーリンク" xfId="12" builtinId="9"/>
     <cellStyle name="良い" xfId="13" builtinId="26"/>
     <cellStyle name="警告文" xfId="14" builtinId="11"/>
     <cellStyle name="リンクセル" xfId="15" builtinId="24"/>
@@ -787,9 +793,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <sheetNames>
       <sheetName val="Stages"/>
-      <sheetName val="StageEvents"/>
       <sheetName val="StageEnemyRates"/>
-      <sheetName val="Tutorials"/>
       <sheetName val="TextData"/>
       <sheetName val="Define"/>
     </sheetNames>
@@ -797,9 +801,7 @@
       <sheetData sheetId="0"/>
       <sheetData sheetId="1"/>
       <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5">
+      <sheetData sheetId="3">
         <row r="1">
           <cell r="D1" t="str">
             <v>Type</v>
@@ -831,169 +833,185 @@
         </row>
         <row r="5">
           <cell r="D5">
-            <v>2010</v>
+            <v>1030</v>
           </cell>
           <cell r="E5" t="str">
-            <v>ダンジョンから出る</v>
+            <v>メインイベント再生</v>
           </cell>
         </row>
         <row r="6">
           <cell r="D6">
-            <v>2020</v>
+            <v>2010</v>
           </cell>
           <cell r="E6" t="str">
-            <v>ダンジョン移動</v>
+            <v>ダンジョンから出る</v>
           </cell>
         </row>
         <row r="7">
           <cell r="D7">
-            <v>2021</v>
+            <v>2011</v>
           </cell>
           <cell r="E7" t="str">
-            <v>移動判定なしでダンジョン移動</v>
+            <v>ダンジョンから出る（確認無し）</v>
           </cell>
         </row>
         <row r="8">
           <cell r="D8">
-            <v>2030</v>
+            <v>2020</v>
           </cell>
           <cell r="E8" t="str">
-            <v>ダンジョンクリア</v>
+            <v>ダンジョン移動</v>
           </cell>
         </row>
         <row r="9">
           <cell r="D9">
-            <v>3010</v>
+            <v>2021</v>
           </cell>
           <cell r="E9" t="str">
-            <v>アーティファクト取得</v>
+            <v>移動判定なしでダンジョン移動</v>
           </cell>
         </row>
         <row r="10">
           <cell r="D10">
-            <v>3020</v>
+            <v>2030</v>
           </cell>
           <cell r="E10" t="str">
-            <v>アイテム取得</v>
+            <v>ダンジョンクリア</v>
           </cell>
         </row>
         <row r="11">
           <cell r="D11">
-            <v>3030</v>
+            <v>3010</v>
           </cell>
           <cell r="E11" t="str">
-            <v>魔法入手</v>
+            <v>アーティファクト取得</v>
           </cell>
         </row>
         <row r="12">
           <cell r="D12">
-            <v>4010</v>
+            <v>3020</v>
           </cell>
           <cell r="E12" t="str">
-            <v>仲間を増やす</v>
+            <v>アイテム取得</v>
           </cell>
         </row>
         <row r="13">
           <cell r="D13">
-            <v>4011</v>
+            <v>3030</v>
           </cell>
           <cell r="E13" t="str">
-            <v>仲間を外す</v>
+            <v>魔法入手</v>
           </cell>
         </row>
         <row r="14">
           <cell r="D14">
-            <v>4020</v>
+            <v>4010</v>
           </cell>
           <cell r="E14" t="str">
-            <v>選択して仲間を増やす</v>
+            <v>仲間を増やす</v>
           </cell>
         </row>
         <row r="15">
           <cell r="D15">
-            <v>5010</v>
+            <v>4011</v>
           </cell>
           <cell r="E15" t="str">
-            <v>強制戦闘</v>
+            <v>仲間を外す</v>
           </cell>
         </row>
         <row r="16">
           <cell r="D16">
-            <v>5020</v>
+            <v>4020</v>
           </cell>
           <cell r="E16" t="str">
-            <v>強制ボス戦闘</v>
+            <v>選択して仲間を増やす</v>
           </cell>
         </row>
         <row r="17">
           <cell r="D17">
-            <v>6010</v>
+            <v>5010</v>
           </cell>
           <cell r="E17" t="str">
-            <v>指定のイベントマスを消す</v>
+            <v>強制戦闘</v>
           </cell>
         </row>
         <row r="18">
           <cell r="D18">
-            <v>6011</v>
+            <v>5020</v>
           </cell>
           <cell r="E18" t="str">
-            <v>指定のイベントマスを表示する</v>
+            <v>強制ボス戦闘</v>
           </cell>
         </row>
         <row r="19">
           <cell r="D19">
-            <v>6020</v>
+            <v>6010</v>
           </cell>
           <cell r="E19" t="str">
-            <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
+            <v>指定のイベントマスを消す</v>
           </cell>
         </row>
         <row r="20">
           <cell r="D20">
-            <v>6030</v>
+            <v>6011</v>
           </cell>
           <cell r="E20" t="str">
-            <v>同フロアの強制戦闘が終わってたらイベントマスを表示する</v>
+            <v>指定のイベントマスを表示する</v>
           </cell>
         </row>
         <row r="21">
           <cell r="D21">
-            <v>7010</v>
+            <v>6020</v>
           </cell>
           <cell r="E21" t="str">
-            <v>ダメージ床</v>
+            <v>同フロアの強制戦闘が終わってたらイベントマスを消す</v>
           </cell>
         </row>
         <row r="22">
           <cell r="D22">
-            <v>7020</v>
+            <v>6030</v>
           </cell>
           <cell r="E22" t="str">
-            <v>怨嗟床</v>
+            <v>同フロアの強制戦闘が終わってたらイベントマスを表示する</v>
           </cell>
         </row>
         <row r="23">
           <cell r="D23">
-            <v>7021</v>
+            <v>7010</v>
           </cell>
           <cell r="E23" t="str">
-            <v>怨嗟床解除</v>
+            <v>ダメージ床</v>
           </cell>
         </row>
         <row r="24">
           <cell r="D24">
-            <v>8010</v>
+            <v>7020</v>
           </cell>
           <cell r="E24" t="str">
-            <v>指定リージョンを開示する</v>
+            <v>怨嗟床</v>
           </cell>
         </row>
         <row r="25">
           <cell r="D25">
+            <v>7021</v>
+          </cell>
+          <cell r="E25" t="str">
+            <v>怨嗟床解除</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="D26">
+            <v>8010</v>
+          </cell>
+          <cell r="E26" t="str">
+            <v>指定リージョンを開示する</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="D27">
             <v>9010</v>
           </cell>
-          <cell r="E25" t="str">
+          <cell r="E27" t="str">
             <v>イベント終了明示</v>
           </cell>
         </row>
@@ -1599,25 +1617,25 @@
         <v>10</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>10</v>
@@ -1667,31 +1685,31 @@
         <v>9</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L5" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>9</v>
@@ -1738,31 +1756,31 @@
         <v>9</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="G6" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L6" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>9</v>
@@ -1809,31 +1827,31 @@
         <v>9</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="J7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="K7" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="L7" s="2" t="s">
         <v>11</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="K7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L7" s="2" t="s">
-        <v>10</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>9</v>
@@ -1880,31 +1898,31 @@
         <v>9</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="J8" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>9</v>
@@ -1951,31 +1969,31 @@
         <v>9</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H9" s="2" t="s">
+      <c r="J9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="I9" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>11</v>
-      </c>
       <c r="K9" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L9" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>9</v>
@@ -2022,25 +2040,25 @@
         <v>9</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K10" s="2" t="s">
         <v>8</v>
@@ -2089,13 +2107,13 @@
         <v>9</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="F11" s="2" t="s">
         <v>12</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>11</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>8</v>
@@ -3889,7 +3907,7 @@
         <v>9</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>9</v>
@@ -3967,10 +3985,10 @@
         <v>9</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>9</v>
@@ -4027,7 +4045,7 @@
         <v>9</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I9" s="2"/>
       <c r="J9" s="2" t="s">
@@ -4150,7 +4168,7 @@
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>9</v>
@@ -5522,7 +5540,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K13"/>
+  <dimension ref="A1:K15"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="7" max="7" width="16.7272727272727" customWidth="1"/>
@@ -5533,34 +5551,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="D1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F1" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H1" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="I1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K1" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -5956,6 +5974,72 @@
         <v>0</v>
       </c>
       <c r="K13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14">
+        <v>63</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <v>3010</v>
+      </c>
+      <c r="F14">
+        <v>5010</v>
+      </c>
+      <c r="G14" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F14,[1]Define!D:D))</f>
+        <v>強制戦闘</v>
+      </c>
+      <c r="H14">
+        <v>-1</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15">
+        <v>63</v>
+      </c>
+      <c r="B15">
+        <v>10</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>3010</v>
+      </c>
+      <c r="F15">
+        <v>5010</v>
+      </c>
+      <c r="G15" t="str">
+        <f>INDEX([1]Define!E:E,MATCH(F15,[1]Define!D:D))</f>
+        <v>強制戦闘</v>
+      </c>
+      <c r="H15">
+        <v>-1</v>
+      </c>
+      <c r="I15">
+        <v>0</v>
+      </c>
+      <c r="J15">
+        <v>0</v>
+      </c>
+      <c r="K15" t="b">
         <v>1</v>
       </c>
     </row>
